--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Pictures/DaraSheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB6E01E-8352-4650-A684-9EB359F38E48}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3BF556-B571-429E-A535-11B55F65C393}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2082,6 +2082,9 @@
   </si>
   <si>
     <t>n9971007</t>
+  </si>
+  <si>
+    <t>https://n9971007:wm$qY@07@test5-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -2448,16 +2451,22 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2467,12 +2476,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2530,6 +2533,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3839,17 +3846,17 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
       <c r="M1" s="64" t="s">
         <v>112</v>
       </c>
@@ -3893,11 +3900,11 @@
       <c r="AQ1" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="AR1" s="50" t="s">
+      <c r="AR1" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="50"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
       <c r="AU1" s="61" t="s">
         <v>374</v>
       </c>
@@ -4282,23 +4289,23 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="P1" s="49"/>
+      <c r="P1" s="50"/>
       <c r="AB1" t="s">
         <v>381</v>
       </c>
@@ -5192,66 +5199,66 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="8"/>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="49" t="s">
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="AQ1" s="49"/>
+      <c r="AQ1" s="50"/>
       <c r="AR1" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AS1" s="54" t="s">
+      <c r="AS1" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54"/>
-      <c r="AW1" s="54"/>
-      <c r="AX1" s="54"/>
-      <c r="AY1" s="54"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
       <c r="AZ1" s="17"/>
       <c r="BA1" s="15" t="s">
         <v>169</v>
@@ -5273,10 +5280,10 @@
       <c r="BP1" s="4"/>
       <c r="BQ1" s="5"/>
       <c r="BR1" s="6"/>
-      <c r="BS1" s="47"/>
-      <c r="BT1" s="47"/>
-      <c r="BU1" s="47"/>
-      <c r="BV1" s="47"/>
+      <c r="BS1" s="52"/>
+      <c r="BT1" s="52"/>
+      <c r="BU1" s="52"/>
+      <c r="BV1" s="52"/>
     </row>
     <row r="2" spans="1:74" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -5711,40 +5718,40 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="51" t="s">
+      <c r="N1" s="50"/>
+      <c r="O1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
       <c r="Z1" s="9"/>
       <c r="AA1" s="9"/>
-      <c r="AB1" s="49" t="s">
+      <c r="AB1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="AC1" s="49"/>
+      <c r="AC1" s="50"/>
       <c r="AD1" s="14" t="s">
         <v>165</v>
       </c>
@@ -5768,10 +5775,10 @@
       <c r="AT1" s="4"/>
       <c r="AU1" s="5"/>
       <c r="AV1" s="6"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
-      <c r="AZ1" s="47"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
     </row>
     <row r="2" spans="1:52" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -6035,18 +6042,18 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="49"/>
+      <c r="K1" s="50"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
@@ -6567,18 +6574,18 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="49"/>
+      <c r="K1" s="50"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
@@ -7573,18 +7580,18 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="49"/>
+      <c r="K1" s="50"/>
       <c r="L1" s="8"/>
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
@@ -8173,70 +8180,70 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="51" t="s">
+      <c r="N1" s="50"/>
+      <c r="O1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="51"/>
-      <c r="BB1" s="51"/>
-      <c r="BC1" s="51"/>
-      <c r="BD1" s="51"/>
-      <c r="BE1" s="51"/>
-      <c r="BF1" s="51"/>
-      <c r="BG1" s="51"/>
-      <c r="BH1" s="51"/>
-      <c r="BI1" s="51"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
+      <c r="BB1" s="53"/>
+      <c r="BC1" s="53"/>
+      <c r="BD1" s="53"/>
+      <c r="BE1" s="53"/>
+      <c r="BF1" s="53"/>
+      <c r="BG1" s="53"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="53"/>
       <c r="BJ1" s="4" t="s">
         <v>160</v>
       </c>
@@ -8247,12 +8254,12 @@
       <c r="BM1" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="BN1" s="47" t="s">
+      <c r="BN1" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="BO1" s="47"/>
-      <c r="BP1" s="47"/>
-      <c r="BQ1" s="47"/>
+      <c r="BO1" s="52"/>
+      <c r="BP1" s="52"/>
+      <c r="BQ1" s="52"/>
     </row>
     <row r="2" spans="1:69" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -8769,70 +8776,70 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="51" t="s">
+      <c r="N1" s="50"/>
+      <c r="O1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="51"/>
-      <c r="BB1" s="51"/>
-      <c r="BC1" s="51"/>
-      <c r="BD1" s="51"/>
-      <c r="BE1" s="51"/>
-      <c r="BF1" s="51"/>
-      <c r="BG1" s="51"/>
-      <c r="BH1" s="51"/>
-      <c r="BI1" s="51"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
+      <c r="BB1" s="53"/>
+      <c r="BC1" s="53"/>
+      <c r="BD1" s="53"/>
+      <c r="BE1" s="53"/>
+      <c r="BF1" s="53"/>
+      <c r="BG1" s="53"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="53"/>
       <c r="BJ1" s="4" t="s">
         <v>160</v>
       </c>
@@ -8843,12 +8850,12 @@
       <c r="BM1" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="BN1" s="47" t="s">
+      <c r="BN1" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="BO1" s="47"/>
-      <c r="BP1" s="47"/>
-      <c r="BQ1" s="47"/>
+      <c r="BO1" s="52"/>
+      <c r="BP1" s="52"/>
+      <c r="BQ1" s="52"/>
       <c r="BS1" t="s">
         <v>644</v>
       </c>
@@ -9581,21 +9588,21 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
@@ -9622,23 +9629,23 @@
       <c r="AL1" s="9"/>
       <c r="AM1" s="9"/>
       <c r="AN1" s="9"/>
-      <c r="AO1" s="52" t="s">
+      <c r="AO1" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="AP1" s="52"/>
+      <c r="AP1" s="54"/>
       <c r="AQ1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="AR1" s="53" t="s">
+      <c r="AR1" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="47" t="s">
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -10037,64 +10044,64 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="51" t="s">
+      <c r="N1" s="50"/>
+      <c r="O1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="49" t="s">
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="AO1" s="49"/>
+      <c r="AO1" s="50"/>
       <c r="AP1" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AQ1" s="54" t="s">
+      <c r="AQ1" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="54"/>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54"/>
-      <c r="AW1" s="54"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
       <c r="AX1" s="17"/>
       <c r="AY1" s="15" t="s">
         <v>169</v>
@@ -10122,10 +10129,10 @@
       <c r="BR1" s="4"/>
       <c r="BS1" s="5"/>
       <c r="BT1" s="6"/>
-      <c r="BU1" s="47"/>
-      <c r="BV1" s="47"/>
-      <c r="BW1" s="47"/>
-      <c r="BX1" s="47"/>
+      <c r="BU1" s="52"/>
+      <c r="BV1" s="52"/>
+      <c r="BW1" s="52"/>
+      <c r="BX1" s="52"/>
     </row>
     <row r="2" spans="1:76" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -10553,57 +10560,57 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
-      <c r="O1" s="50" t="s">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>375</v>
       </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
-      <c r="Z1" s="50"/>
-      <c r="AA1" s="50"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
       <c r="AB1" s="20"/>
       <c r="AC1" s="20"/>
       <c r="AD1" s="20"/>
       <c r="AE1" s="20"/>
       <c r="AF1" s="20"/>
       <c r="AG1" s="20"/>
-      <c r="AH1" s="49" t="s">
+      <c r="AH1" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="AI1" s="49"/>
+      <c r="AI1" s="50"/>
       <c r="AJ1" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AK1" s="54" t="s">
+      <c r="AK1" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AL1" s="54"/>
-      <c r="AM1" s="55" t="s">
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="47" t="s">
         <v>419</v>
       </c>
-      <c r="AN1" s="55"/>
+      <c r="AN1" s="47"/>
       <c r="AO1" s="48" t="s">
         <v>422</v>
       </c>
@@ -11058,21 +11065,21 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
@@ -11100,21 +11107,21 @@
       <c r="AM1" s="8"/>
       <c r="AN1" s="8"/>
       <c r="AO1" s="8"/>
-      <c r="AP1" s="49" t="s">
+      <c r="AP1" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="AQ1" s="49"/>
+      <c r="AQ1" s="50"/>
       <c r="AR1" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AS1" s="54" t="s">
+      <c r="AS1" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="55" t="s">
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="47" t="s">
         <v>419</v>
       </c>
-      <c r="AV1" s="55"/>
+      <c r="AV1" s="47"/>
       <c r="AW1" s="48" t="s">
         <v>422</v>
       </c>
@@ -11280,7 +11287,7 @@
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>602</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>675</v>
@@ -11464,9 +11471,10 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{49C049CF-31D2-4B3F-ACD5-8D464591EDCA}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{884DC742-00AB-44A2-A3B7-419C589B09C0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -11484,21 +11492,21 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
@@ -11526,21 +11534,21 @@
       <c r="AM1" s="8"/>
       <c r="AN1" s="8"/>
       <c r="AO1" s="8"/>
-      <c r="AP1" s="49" t="s">
+      <c r="AP1" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="AQ1" s="49"/>
+      <c r="AQ1" s="50"/>
       <c r="AR1" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AS1" s="54" t="s">
+      <c r="AS1" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="55" t="s">
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="47" t="s">
         <v>419</v>
       </c>
-      <c r="AV1" s="55"/>
+      <c r="AV1" s="47"/>
       <c r="AW1" s="48" t="s">
         <v>422</v>
       </c>
@@ -11891,65 +11899,65 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="51" t="s">
+      <c r="L1" s="50"/>
+      <c r="M1" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51" t="s">
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53" t="s">
         <v>273</v>
       </c>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="49" t="s">
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="AV1" s="49"/>
-      <c r="AW1" s="52" t="s">
+      <c r="AV1" s="50"/>
+      <c r="AW1" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="AX1" s="52"/>
+      <c r="AX1" s="54"/>
       <c r="BF1" s="56" t="s">
         <v>165</v>
       </c>
@@ -12462,21 +12470,21 @@
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="49" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="N1" s="49"/>
+      <c r="N1" s="50"/>
       <c r="O1" s="58" t="s">
         <v>113</v>
       </c>
@@ -12513,12 +12521,12 @@
       <c r="AL1" s="57"/>
       <c r="AM1" s="57"/>
       <c r="AN1" s="57"/>
-      <c r="AO1" s="50" t="s">
+      <c r="AO1" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="AP1" s="50"/>
-      <c r="AQ1" s="50"/>
-      <c r="AR1" s="50"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
     </row>
     <row r="2" spans="1:44" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">

--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3BF556-B571-429E-A535-11B55F65C393}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0BA118-162F-4D2D-AC35-99B381E1257A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2084,7 +2084,7 @@
     <t>n9971007</t>
   </si>
   <si>
-    <t>https://n9971007:wm$qY@07@test5-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971007:wm$qY@07@stage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>

--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A0BA118-162F-4D2D-AC35-99B381E1257A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7545AC03-C321-4527-A176-4563B8CBC7EC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="678">
   <si>
     <t>First Named Insured</t>
   </si>
@@ -2084,7 +2084,10 @@
     <t>n9971007</t>
   </si>
   <si>
-    <t>https://n9971007:wm$qY@07@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971007:wm$qY@07@test5-underwritingplatform.grsazr.lmig.com</t>
+  </si>
+  <si>
+    <t>11/11/2026</t>
   </si>
 </sst>
 </file>
@@ -2535,10 +2538,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -11434,7 +11433,7 @@
         <v>373</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AY3" t="s">
         <v>21</v>

--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7545AC03-C321-4527-A176-4563B8CBC7EC}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CF0C78-D960-4DCB-A403-30012190D445}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2084,10 +2084,10 @@
     <t>n9971007</t>
   </si>
   <si>
-    <t>https://n9971007:wm$qY@07@test5-underwritingplatform.grsazr.lmig.com</t>
-  </si>
-  <si>
     <t>11/11/2026</t>
+  </si>
+  <si>
+    <t>https://n9971007:wm$qY@07@stage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -2538,6 +2538,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -11286,7 +11290,7 @@
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B3" t="s">
         <v>675</v>
@@ -11433,7 +11437,7 @@
         <v>373</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AY3" t="s">
         <v>21</v>

--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CF0C78-D960-4DCB-A403-30012190D445}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0EF1341-3B49-4A47-8140-84D4B186308C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2087,7 +2087,7 @@
     <t>11/11/2026</t>
   </si>
   <si>
-    <t>https://n9971007:wm$qY@07@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971007:wm$qY@07@hfstage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>

--- a/usproperty/DataSheet.xlsx
+++ b/usproperty/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/usproperty/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57CF0C78-D960-4DCB-A403-30012190D445}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="6_{25188133-A159-4555-AAC1-BE82FE66A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7767579A-0C6F-43E3-94E0-B92F016C4A73}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="5" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2087,7 +2087,7 @@
     <t>11/11/2026</t>
   </si>
   <si>
-    <t>https://n9971007:wm$qY@07@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971007:wm$qY@07@test-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
